--- a/artfynd/A 57986-2025 artfynd.xlsx
+++ b/artfynd/A 57986-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>82766027</v>
+        <v>82766023</v>
       </c>
       <c r="B2" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>606244.2022119779</v>
+        <v>606531</v>
       </c>
       <c r="R2" t="n">
-        <v>6675612.814784456</v>
+        <v>6675528</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,19 +747,9 @@
           <t>2019-06-12</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-06-12</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -797,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>82766030</v>
+        <v>82766026</v>
       </c>
       <c r="B3" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -841,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>606232.0671856567</v>
+        <v>606235</v>
       </c>
       <c r="R3" t="n">
-        <v>6675412.987294408</v>
+        <v>6675619</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,19 +854,9 @@
           <t>2019-06-12</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2019-06-12</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -919,15 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>82766026</v>
+        <v>82766027</v>
       </c>
       <c r="B4" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -963,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>606235.0534903527</v>
+        <v>606244</v>
       </c>
       <c r="R4" t="n">
-        <v>6675619.015695124</v>
+        <v>6675613</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,19 +961,9 @@
           <t>2019-06-12</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2019-06-12</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1041,15 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>82766031</v>
+        <v>82766029</v>
       </c>
       <c r="B5" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1085,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>606263.8724604701</v>
+        <v>606228</v>
       </c>
       <c r="R5" t="n">
-        <v>6675450.225173988</v>
+        <v>6675399</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1118,19 +1068,9 @@
           <t>2019-06-12</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2019-06-12</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1163,15 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>82766029</v>
+        <v>82766030</v>
       </c>
       <c r="B6" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1207,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>606227.990475499</v>
+        <v>606232</v>
       </c>
       <c r="R6" t="n">
-        <v>6675398.940086028</v>
+        <v>6675413</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1240,19 +1175,9 @@
           <t>2019-06-12</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2019-06-12</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1285,15 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>82766039</v>
+        <v>82766031</v>
       </c>
       <c r="B7" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1329,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>606257.869259715</v>
+        <v>606264</v>
       </c>
       <c r="R7" t="n">
-        <v>6675451.045719941</v>
+        <v>6675450</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1362,19 +1282,9 @@
           <t>2019-06-12</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2019-06-12</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1410,12 +1320,7 @@
         <v>82766035</v>
       </c>
       <c r="B8" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1451,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>606480.1186448658</v>
+        <v>606480</v>
       </c>
       <c r="R8" t="n">
-        <v>6675536.104274143</v>
+        <v>6675536</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1484,19 +1389,9 @@
           <t>2019-06-12</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2019-06-12</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1526,6 +1421,327 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>82766036</v>
+      </c>
+      <c r="B9" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Tistelberget, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>606501</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6675563</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2019-06-12</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2019-06-12</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Rikliga bestånd</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Nike Nylander</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Nike Nylander</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>82766038</v>
+      </c>
+      <c r="B10" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Tistelberget, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>606404</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6675582</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2019-06-12</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2019-06-12</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rikliga bestånd</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Nike Nylander</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Nike Nylander</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>82766039</v>
+      </c>
+      <c r="B11" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Tistelberget, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>606258</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6675451</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2019-06-12</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2019-06-12</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Rikliga bestånd</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Nike Nylander</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Nike Nylander</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
